--- a/polls/008_groundhog_day_opinion_poll--polls.xlsx
+++ b/polls/008_groundhog_day_opinion_poll--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_source</t>
+          <t>groundhog_day_survey_source_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you participate in surveys</t>
+          <t>Groundhog Day Survey Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>groundhog_day_education</t>
+          <t>groundhog_day_education_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How did you learn about Groundhog Day</t>
+          <t>Groundhog Day Education 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency</t>
+          <t>groundhog_day_frequency_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How often do you participate in surveys</t>
+          <t>Groundhog Day Frequency 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>groundhog_day_education</t>
+          <t>groundhog_day_education_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How did you learn about Groundhog Day</t>
+          <t>Groundhog Day Education 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency</t>
+          <t>groundhog_day_frequency_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How often do you get weather information on Groundhog Day</t>
+          <t>Groundhog Day Frequency 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>groundhog_day_education_2</t>
+          <t>groundhog_day_education_2_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How did you learn about Groundhog Day</t>
+          <t>Groundhog Day Education 2 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>groundhog_day_education_3</t>
+          <t>groundhog_day_education_3_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How did you learn about Groundhog Day</t>
+          <t>Groundhog Day Education 3 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_2</t>
+          <t>groundhog_day_frequency_2_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How often do you get weather information on Groundhog Day</t>
+          <t>Groundhog Day Frequency 2 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_education</t>
+          <t>groundhog_day_survey_education_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How do you usually get information about surveys</t>
+          <t>Groundhog Day Survey Education Source</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>groundhog_day_additional_notes</t>
+          <t>groundhog_day_additional_notes_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Groundhog Day Additional Notes 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_source_choices</t>
+          <t>groundhog_day_survey_source_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_source_choices</t>
+          <t>groundhog_day_survey_source_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_source_choices</t>
+          <t>groundhog_day_survey_source_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_source_choices</t>
+          <t>groundhog_day_survey_source_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_source_choices</t>
+          <t>groundhog_day_survey_source_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_3_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_3_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_3_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_3_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>groundhog_day_education_choices</t>
+          <t>groundhog_day_education_3_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_3_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_3_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_3_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_choices</t>
+          <t>groundhog_day_frequency_3_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>groundhog_day_education_2_choices</t>
+          <t>groundhog_day_education_2_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>groundhog_day_education_2_choices</t>
+          <t>groundhog_day_education_2_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>groundhog_day_education_2_choices</t>
+          <t>groundhog_day_education_2_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>groundhog_day_education_2_choices</t>
+          <t>groundhog_day_education_2_2_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>groundhog_day_education_2_choices</t>
+          <t>groundhog_day_education_2_2_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>groundhog_day_education_3_choices</t>
+          <t>groundhog_day_education_3_2_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>groundhog_day_education_3_choices</t>
+          <t>groundhog_day_education_3_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>groundhog_day_education_3_choices</t>
+          <t>groundhog_day_education_3_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>groundhog_day_education_3_choices</t>
+          <t>groundhog_day_education_3_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>groundhog_day_education_3_choices</t>
+          <t>groundhog_day_education_3_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_2_choices</t>
+          <t>groundhog_day_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_2_choices</t>
+          <t>groundhog_day_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_2_choices</t>
+          <t>groundhog_day_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>groundhog_day_frequency_2_choices</t>
+          <t>groundhog_day_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_education_choices</t>
+          <t>groundhog_day_survey_education_2_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2486,7 +2486,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_education_choices</t>
+          <t>groundhog_day_survey_education_2_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2503,7 +2503,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_education_choices</t>
+          <t>groundhog_day_survey_education_2_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2520,7 +2520,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_education_choices</t>
+          <t>groundhog_day_survey_education_2_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2537,7 +2537,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>groundhog_day_survey_education_choices</t>
+          <t>groundhog_day_survey_education_2_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
